--- a/text/foundationScores/shapessocial_6_seconds_MFT_MAC.xlsx
+++ b/text/foundationScores/shapessocial_6_seconds_MFT_MAC.xlsx
@@ -425,166 +425,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG40"/>
+  <dimension ref="A1:AI40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>chunkEnd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chunkStart</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>V_neu</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>V_neg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>V_pos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>V_com</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>full_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_virtue</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_virtue</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_virtue</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_virtue</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_vice</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_vice</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_vice</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_vice</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_vice</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_moral_nonmoral</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_virtue</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_virtue</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_virtue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_virtue</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_virtue</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_virtue</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_vice</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_vice</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_vice</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_vice</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_vice</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_vice</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_vice</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_moral_nonmoral</t>
         </is>
@@ -594,104 +604,114 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10.544</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>76</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>24</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>45.88</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Let's all go to the lobby.  Let's all go to the lobby.  Let's all go to the lobby to get ourselves a treat.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.07627118644067797</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0.06818181818181818</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0217391304347826</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.03525641025641026</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.1271186440677966</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.09274193548387097</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.08891752577319588</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.06683168316831684</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.07774390243902438</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>0.06428571428571428</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>0.08695652173913043</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.3491758241758242</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>0.05978260869565218</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>0.2523726273726274</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>0.1751644736842105</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>0.02142857142857143</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>0.19</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>0.1704545454545454</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0.1097560975609756</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
       <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0.05434782608695653</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>1.333333333333333</v>
       </c>
     </row>
@@ -699,104 +719,114 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>19.616</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12.166</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>68.8</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>31.2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>70.96000000000001</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Delicious things to eat.  The popcorn can't be beat.  The sparkling drinks are just dandy.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.07751937984496123</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.03846153846153847</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.07109799838019205</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.02729885057471264</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.1122073447654843</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.05061250805931657</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.01801801801801802</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.06346826586706646</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.13955463728191</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.6</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.06832298136645963</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.06725146198830409</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.1</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0.1606263982102908</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>0.06521739130434782</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>0.1497524752475247</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>0.08</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>0.07777777777777778</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>0.05921052631578947</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0.125</v>
       </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -804,34 +834,38 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26.224</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>19.996</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>93.2</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>6.800000000000001</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>2.58</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">  The chocolate bars and the candy.  So let's all go to the lobby to get ourselves</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -842,66 +876,72 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.1694915254237288</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.1236559139784946</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.1185567010309278</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.0891089108910891</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.1036585365853658</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.25</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
         <v>0.3367724867724868</v>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>0.1233766233766234</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>0.07291666666666667</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0.2457142857142857</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>0.2088744588744589</v>
       </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
         <v>0.1044207317073171</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
       <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0.1725955204216074</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -909,104 +949,114 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>49.519</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30.811</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>7.5</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>21.3</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>51.06</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve"> To get ourselves a treat A young boy carrying a ball goes to an empty playground to play by himself.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.06033255247806715</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.07358818855665851</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.08042533473939859</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.03444580526638089</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.04073724680160324</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.08442716084234658</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.04244827095394618</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.03200693497618206</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>0.06742302249548626</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.05467836257309942</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>3</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.08698412698412698</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.1348350586611456</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.06276923076923077</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>0.07639751552795031</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>0.1011188811188811</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>0.1398110661268556</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>0.03819548872180451</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
         <v>0.0822426267804419</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>0.07333842627960276</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
         <v>0.1283580573054257</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>0.08811194202451622</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.06986324786324785</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.0583224115334207</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>0.06897635300175603</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>1.666666666666667</v>
       </c>
     </row>
@@ -1014,104 +1064,114 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>61.302</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>100</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy kicks the ball and then dashes after it.  He lines up his shot and kicks the ball again.  The boy catches up to the ball and bounces it off the playground's fences several times, passing it to himself.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.0126984126984127</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.07886302294197031</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.1566148607052507</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.06081063701443836</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.02830173049363388</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.1094594172734309</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.08879128700024295</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.6</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.03645833333333334</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.03134796238244514</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.05172413793103448</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.02840909090909091</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>0.03423167057248075</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.025</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>0.035</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>0.1619736842105263</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>0.09513805522208885</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
         <v>0.1812307567655161</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>0.0907123447204969</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>0.1104425465838509</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.06007051943584452</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.01171875</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -1119,104 +1179,114 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>68.763</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>62.705</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>100</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve"> As he circles the ball, lining up his next shot, His father shows up and calls for him.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.01612903225806452</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.04723355430902601</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.07152349200868902</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.1177634247756199</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.07691577748724221</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.03104575163398693</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>0.1002369313165853</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.0910304980338619</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>0.04583333333333333</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.021875</v>
       </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.03985507246376811</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>0.152141548327989</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>0.01851851851851852</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>0.1456066012488849</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>0.1600840336134454</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>0.119139304428668</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>0.1476324038937469</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.1154717484008529</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.04837461300309598</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.04411164446185998</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>1.333333333333333</v>
       </c>
     </row>
@@ -1224,104 +1294,114 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>76.313</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>68.783</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>95.89999999999999</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>4.100000000000001</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>-5.16</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy takes one final kick at the ball before leaving the playground to meet his waiting father.  The boy and his father exchange a few words and leave.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.05226963432848582</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.04872751501364508</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.05005376513279285</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.01335164193058315</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.01070763500931099</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.05987324826456821</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.04700569685313685</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.04901968690665195</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>0.07041822092109738</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.06829566695030344</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0.08243825758213158</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.02</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>0.04559634038800706</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>0.07414707952342361</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>0.08812792851694454</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>0.1581440414773748</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>0.03901991614255765</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>0.05882295400949632</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>0.1529197136044661</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>0.05775549564614346</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>0.09122553859395964</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.07059780497280498</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.06509062253743106</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.06911018351774038</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -1329,104 +1409,114 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>88.189</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>76.674</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>100</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy and his father live in a modest two-story home with a pointed roof.  After arriving home, they have a short chat, and the boy turns and climbs the stairs to his second-floor bedroom.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.02836468615331094</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.03127622850151977</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.0462965331146997</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.01422413793103448</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>0.02220923931450247</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.0799517244921495</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0.06724236904340947</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.02063403525460861</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>0.06766110970204973</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.05448988977389574</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>0.09001104367567711</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.1005669213608303</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>0.05496748607587554</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>0.2146054384860356</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>0.1094987995198079</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>0.07121374865735768</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>0.1688289861035641</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>0.02448979591836735</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>0.1117586667106386</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>0.06216630891955567</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.007792207792207792</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.04281738669493772</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>0.6363636363636364</v>
       </c>
     </row>
@@ -1434,104 +1524,114 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>108.748</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>93.822</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>93.30000000000001</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>6.7</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>42.15</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">  His father follows, gives his son a goodnight kiss and tucks him in for the night.  While the boy falls asleep, his father walks back downstairs to his bedroom on the first floor, climbs into bed and quickly falls asleep.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.01433691756272401</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.05429769392033543</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.05161053858824819</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>0.09022511931775214</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>0.03140440012339066</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.007147498375568552</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>0.06646307002222794</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.06510624929574821</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.75</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>0.05741699664940603</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>0.02414486921529175</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>0.0506593865616422</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>0.07695578231292517</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>0.1256456405912928</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>0.3349818000980792</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>0.07365253793825222</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AB10" t="n">
         <v>0.04148175316339629</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
         <v>0.1354218968446055</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AD10" t="n">
         <v>0.04363180678970153</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>0.08698206555349412</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.006802721088435374</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.005952380952380952</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.0566017316017316</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1539,88 +1639,92 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>119.526</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>110.731</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>81.5</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>18.5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>51.06</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">  Upstairs, the boy begins to dream.  The ceiling opens up and he floats into the sky along with a huge bird.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.04289194855232591</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.06542744486329563</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.1017232837541966</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.05694150810429879</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>0.06020775916896332</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>0.06</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.01492537313432836</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.04242424242424242</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.325</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>0.03773584905660377</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>0.1016949152542373</v>
       </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>0.07547169811320754</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
@@ -1637,6 +1741,12 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -1644,104 +1754,114 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>132.925</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>122.543</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>100</v>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">  High above mountains, the boy can fly.  The giant bird splits into two smaller birds which soar across the sky with the boy.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.006896551724137929</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.02758620689655172</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.04912280701754386</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.02420749279538905</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>0.02427745664739884</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.1042214076246334</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.07252324237398865</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.06756651258346173</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.1129461279461279</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.08284600389863547</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
         <v>0.2207792207792208</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.1503267973856209</v>
       </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AB12" t="n">
         <v>0.3306451612903226</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
       <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
         <v>0.1304347826086956</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>0.2</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.1121495327102804</v>
       </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
         <v>0.09090909090909091</v>
       </c>
     </row>
@@ -1749,67 +1869,71 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>142.947</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>135.554</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>93.89999999999999</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>6.1</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>12.8</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">  The two birds become four birds.  The boy plays with the birds, but then the flock gangs up on him and starts chasing him.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>0.06140350877192983</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>0.2358333333333333</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>0.1223880597014925</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.1041666666666667</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>0.06363636363636363</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.1326315789473684</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
@@ -1847,6 +1971,12 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1854,104 +1984,114 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>152.524</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>143.188</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>59.59999999999999</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>20.2</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>20.2</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>24.41</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">  He tries to fly away but cannot escape.  Thankfully, the dream ends and the birds disappear.  The boy sleeps peacefully for the rest of the night.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.06630759448749041</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.06097881345971586</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.04612737127758326</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.04718432751219637</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>0.04749297735351878</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.0556679163487166</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.06033874292167507</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.04908371390326491</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.09687816045502499</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.05981994921491098</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>1.8</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.06818181818181819</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>0.05128205128205129</v>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>0.05454545454545454</v>
       </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
         <v>0.09206349206349207</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>0.1749500300432868</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>0.1576813499890423</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>0.1436507936507937</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>0.09155328798185941</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>0.1007069494464452</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AF14" t="n">
         <v>0.05691056910569106</v>
       </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0.06194690265486726</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>0.2727272727272727</v>
       </c>
     </row>
@@ -1959,104 +2099,114 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>169.489</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>154.688</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>100</v>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">  In the morning, the boy's father climbs the stairs to his son's bedroom and wakes him up.  The boy follows his father down the stairs to the first floor of their home.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.01612903225806452</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.04858490566037736</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.05745829033367734</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0.01932695682695683</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>0.08835851287899281</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.04536072574794832</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.01858056467757364</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>0.07480798026878045</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.06744959376636282</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.06561016689634053</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
         <v>0.08478557504873294</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>0.1175533272096346</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>0.4296710375502462</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>0.1081555699202758</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AB15" t="n">
         <v>0.05807445442875481</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>0.1958816111564424</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>0.03684210526315789</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="n">
         <v>0.1278195236497819</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
         <v>0.009523809523809523</v>
       </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.02424242424242424</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.5555555555555556</v>
       </c>
     </row>
@@ -2064,104 +2214,114 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>185.032</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>169.709</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>100</v>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">  They have a brief conversation before the boy heads out for the day.  The day passes.  The father waits for his son to return home.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.0162387535659425</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.01709593690725766</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.04799430897311346</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0.02343482983617244</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.0759708779092782</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.04317970646873071</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.0235336013508257</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>0.05837311522888993</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.04582470826568141</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.04969887204613892</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>0.02704081632653061</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.07956757155831926</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>0.0311854103343465</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>0.08726021021064713</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>0.2712678483244259</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>0.06934851018250895</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>0.06726553442282319</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>0.09842383990166055</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
         <v>0.06831219425366795</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
         <v>0.02173913043478261</v>
       </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0.008658008658008658</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -2169,104 +2329,114 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>192.683</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>185.833</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>100</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">  When he does, the two talk briefly.  The boy climbs into bed as does his father downstairs.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.01290322580645161</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.05192176389282086</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.06272373821009433</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.02085308056872038</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>0.01271676300578035</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.1336728763489479</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>0.008955223880597014</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.01714285714285715</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.03858585858585858</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.05588629107014111</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>2.5</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.03070175438596491</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.03864734299516908</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>0.1057432432432432</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>0.1000884534258692</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>0.3248892960757368</v>
       </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
         <v>0.02807017543859649</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>0.09803921568627451</v>
       </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
         <v>0.1492626614577834</v>
       </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
       <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0.0372960372960373</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -2274,104 +2444,114 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>202.521</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>192.904</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>80.60000000000001</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>8.6</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>10.8</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>10.27</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">  Both fall right asleep.  Shortly after falling asleep, the boy starts to have the bird dream again.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.0421192338044336</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.05020275211061622</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.07050141137204352</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.0393354868481772</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>0.02264150943396227</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.09135714285714286</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.02269568189586419</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.04222222222222222</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.04610454545454545</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.1012771031068686</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.1796157059314954</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.1076190476190476</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.1645718116306352</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>0.06511627906976744</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>0.06008583690987124</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>0.1094017094017094</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>0.04385964912280702</v>
       </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AF18" t="n">
         <v>0.02424242424242424</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AG18" t="n">
         <v>0.04972375690607735</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AH18" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AI18" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -2379,104 +2559,114 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>210.448</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>202.882</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>84.89999999999999</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>9.700000000000001</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>5.4</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>0.67</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">  The four birds from the previous night are back.  They surround him, preventing him from escaping no matter which direction he turns.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.06814983597310256</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.1323733416697603</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>0.01713709677419355</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>0.1276406225170825</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>0.07586286919831223</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.02960526315789474</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.05576923076923077</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>0.09015100292990759</v>
       </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>0.04132231404958678</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>0.04</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>0.08425448292802751</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
         <v>0.04494111992309541</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AA19" t="n">
         <v>0.0398989898989899</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AB19" t="n">
         <v>0.02339181286549707</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>0.08223169864960909</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>0.08950617283950617</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="n">
         <v>0.02710027100271003</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
         <v>0.04444444444444445</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AH19" t="n">
         <v>0.03809523809523809</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2484,104 +2674,114 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>220.294</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>213.787</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>100</v>
       </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">  The birds transform into a giant monster with two long arms and two wobbly legs.  The monster swats at the boy.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.03690023537932283</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.04432884536923705</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.016</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>0.02666666666666666</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>0.1917184346322987</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>0.07490792356823647</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>0.0585</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>0.0993585937658852</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>0.07326146692031282</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
         <v>0.09523809523809523</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
       <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>0.09731543624161074</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>0.1229763387297634</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>0.05298013245033113</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>0.2165372316126085</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>0.07489878542510121</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>0.09836065573770492</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
         <v>0.1383458646616541</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AF20" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.2222222222222222</v>
       </c>
     </row>
@@ -2589,104 +2789,114 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>228.904</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>220.755</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>80.60000000000001</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>19.4</v>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>-58.59</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">  He misses and tries again.  Frightened, the boy flies over the monster, evading its grasp.  The monster scrunches into a little ball.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.0625</v>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>0.0711578947368421</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.02168021680216803</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>0.04545454545454545</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>0.0897790585975024</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>0.147764033712715</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>0.0617283950617284</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>0.1217893217893218</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>0.06338960609069844</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
         <v>0.07017543859649122</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>0.1409395973154362</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>0.1491228070175439</v>
       </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
         <v>0.1849315068493151</v>
       </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.125</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.05797101449275362</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.09090909090909091</v>
       </c>
     </row>
@@ -2694,104 +2904,114 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>238.495</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>229.104</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>11.7</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>11</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>-5.800000000000001</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">  It pounces, lunging at the boy.  After the boy dodges this attack, the nightmare finally ends.  The boy sleeps peacefully for the rest of the night.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.05137066541705718</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.05541009016409474</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.07088342514039109</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.04626418663303909</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>0.0278638322116583</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>0.1116358024691358</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>0.03529753828261291</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.01824324324324324</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>0.08096843812478574</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.06129750131698673</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>0.1198863636363637</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>0.03846153846153846</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>0.04090909090909091</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.05102040816326531</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.08301158301158301</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>0.08446455505279035</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>0.05</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>0.1273148148148148</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>0.1642793227849899</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>0.1374188311688312</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AE22" t="n">
         <v>0.08184925346285303</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
         <v>0.08569367951744034</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>0.05322128851540616</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>0.05248846407382993</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2799,104 +3019,114 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>250.22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>242.609</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>100</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">  In the morning, the boy's dad wakes up, walks to the stairs and shouts for his son to come down.  The boy jumps up and goes down the stairs.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.01601489757914339</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>0.01391304347826087</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.08499190507120628</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.01946564885496183</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>0.02090268886043534</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>0.1066650392000376</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>0.05621666463161717</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>0.01286549707602339</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>0.08025691699604742</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.06247563352826511</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>0.625</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
         <v>0.04</v>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>0.03490401396160558</v>
       </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
         <v>0.08572247706422019</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.3857697659128786</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>0.02936395574432384</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>0.1642331729439743</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>0.1028490028490028</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>0.1023391812865497</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>0.1240378343118069</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>0.04273504273504273</v>
       </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0.02702702702702703</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2904,104 +3134,114 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>272.926</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>252.744</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>84.89999999999999</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
         <v>15.1</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>65.97</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">  After a brief good morning, the boy again heads out for the day and the day passes.  At the end of the day, the boy returns home, greets his father quickly, and then goes straight upstairs to his bedroom.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.01349344543077967</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.02754451128018161</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.05220679187364292</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.01139440829963074</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>0.02895539611711521</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>0.07215700472114601</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>0.02788771619602463</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>0.01868281007666391</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.05770125185682311</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.03702861732557287</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>1.857142857142857</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.04745696313004467</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.05079954474320672</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.06253349029685054</v>
       </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
         <v>0.04388842359947888</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>0.07962068026444641</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>0.113621380597757</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>0.04079594485019986</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>0.05260888268407065</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>0.07586529354248737</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>0.03116027616935058</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AE24" t="n">
         <v>0.06200289739446559</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>0.02529795199952268</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AG24" t="n">
         <v>0.01306844819503047</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
         <v>0.05618804192102621</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.8181818181818182</v>
       </c>
     </row>
@@ -3009,104 +3249,114 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>284.76</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>275.609</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>92.60000000000001</v>
       </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
         <v>7.399999999999999</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>25</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy climbs into bed, as does his father downstairs.  Both eventually fall asleep.  For the third night in a row, the boy begins to dream.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.02763998782714547</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.0244475148549986</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.05709910910249941</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.02287322768974145</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.04068547025044636</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.1029117063492063</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>0.04478181611028825</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>0.01726726726726727</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.04902525252525252</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.05250776979021566</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>1.6</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.07738095238095238</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.03</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>0.07628676470588236</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>0.046875</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>0.07457729468599034</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.2502945252945253</v>
       </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
         <v>0.02105263157894737</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>0.1003151260504202</v>
       </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
         <v>0.1005140692640693</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>0.01818181818181818</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AG25" t="n">
         <v>0.03409090909090909</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>0.07969399881164588</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.4444444444444444</v>
       </c>
     </row>
@@ -3114,104 +3364,114 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>295.132</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>288.705</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
         <v>17.4</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>42.15</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve"> The towering monster from the previous dream appears again, slowly following the boy and reaching for him with one arm.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.009433962264150943</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.02269635126777983</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.0638262340074882</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.03656490539692639</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.02269934215282296</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.08508802981979256</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.03752970596751691</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.01412429378531073</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.05039679421701893</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>0.03969448121249605</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>1.5</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.1423728813559322</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.2003918495297806</v>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>0.01923076923076923</v>
       </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>0.1083622117534292</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.03947368421052631</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>0.02832167832167832</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>0.03867062021250309</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>0.03928571428571428</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>0.0418613707165109</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>0.1377389971139971</v>
       </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
         <v>0.01102941176470588</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>0.04880952380952381</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -3219,104 +3479,114 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>304.709</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>295.913</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>84.39999999999999</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>10.7</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>4.9</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>-31.82</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy stays out of his reach and hovers uncertainly around the monster's feet.  Suddenly he is joined by another boy.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.02173941410582632</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>0.03372050816696914</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.04912280701754386</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.01746031746031746</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.02068256194483404</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.09240816326530613</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.02791044776119403</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.05248467286138518</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>0.0942297015961138</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.05719960278053624</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.1090909090909091</v>
       </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
         <v>0.1816326530612245</v>
       </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>0.1399915540540541</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>0.07317073170731707</v>
       </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>0.1807256235827664</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
         <v>0.1584766584766585</v>
       </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
         <v>0.1346153846153846</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.05102040816326531</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -3324,104 +3594,114 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>311.998</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>304.749</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>10.6</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>5.3</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>-29.6</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boys speak frantically as the monster reaches down.  The boys fly over the monster which is still clawing at them.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.026765850945495</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>0.03448275862068965</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.07919254658385093</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
         <v>0.08823529411764706</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.07113821138211382</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.06293706293706294</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.0462962962962963</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.128598661686897</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>0.8</v>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
         <v>0.2244897959183673</v>
       </c>
-      <c r="U28" t="n">
+      <c r="W28" t="n">
         <v>0.2</v>
       </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
       <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
         <v>0.2549019607843137</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>0.1219512195121951</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
         <v>0.125</v>
       </c>
     </row>
@@ -3429,104 +3709,114 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>320.669</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>312.719</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>91.60000000000001</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>8.4</v>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
         <v>-31.82</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boys make a desperate plan and the new boy speeds away.  He quickly returns with the ball.  The boys pull the ball in a slingshot.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.008069164265129682</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.03919777174072235</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.02719835592798212</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.03057732779054528</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>0.01412842676363778</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.09425622337521808</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.05760279556350638</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.06589700484783781</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.05787911944377462</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.07728588629870843</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>2.5</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.01119402985074627</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.08291617172917021</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>0.03174603174603174</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.1084651350292362</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>0.1029749320446995</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>0.06249599897573779</v>
       </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
         <v>0.1113665293780797</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>0.07205788804071248</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>0.09980199766139675</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>0.05102040816326531</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>0.0341726618705036</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>0.02048860911270983</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>0.1619086539527853</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -3534,104 +3824,114 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>328.219</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>320.85</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>89</v>
       </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
         <v>11</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>47.67</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">  But the last minute they let it go, shooting the ball into the monster which breaks into a heap.  Excited, the boy swoops over the heap.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>0.04093567251461989</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.194575253219321</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>0.07764938747124592</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.0737069345316768</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>0.1041784947725542</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.1056766008627369</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>0.375</v>
       </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
       <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
         <v>0.2071428571428572</v>
       </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
         <v>0.1233766233766234</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>0.07291666666666667</v>
       </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
         <v>0.1674829931972789</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>0.2214795008912656</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>0.05952380952380952</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>0.2270168855534709</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
         <v>0.125</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>0.06122448979591837</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>0.09575569358178054</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>0.2222222222222222</v>
       </c>
     </row>
@@ -3639,104 +3939,114 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>342.505</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>331.692</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>90</v>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
         <v>10</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>27.32</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">  until he notices that the other boy is gone.  He goes looking for his new friend but can't find him.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.02480056903102659</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>0.05662523242103765</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.06721009907738519</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.02857978717586972</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>0.02465161344387443</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>0.0628069229713142</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>0.02429770340218101</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.03554282596835789</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>0.04991780410986341</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.03639001349527665</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>6</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>0.024</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>0.07498039215686274</v>
       </c>
-      <c r="U31" t="n">
+      <c r="W31" t="n">
         <v>0.03895348837209302</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>0.02980536106768178</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>0.08601630927212323</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>0.1257246376811594</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>0.02927234927234927</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>0.1367133466926834</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>0.06717895648067992</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>0.06945467116066026</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>0.06113100382763303</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>0.05376602564102564</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>0.03574986164914222</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>0.05086823086823087</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -3744,104 +4054,114 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>351.356</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>342.986</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
         <v>11.6</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>27.32</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">  He checks under the rubble for his friend.  He finds the ball, but not the other boy.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.01734104046242774</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>0.02579365079365079</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.06712559544556757</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.02586206896551724</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>0.0297841726618705</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.1121296296296296</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>0.06786069651741293</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>0.1226172132951794</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.04904306220095694</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>2</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.4830769230769231</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>0.1274509803921569</v>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>0.09738372093023256</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>0.03191489361702127</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>0.2155844155844156</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>0.1875</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.02702702702702703</v>
       </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
         <v>0.09523809523809523</v>
       </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>0.08</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3849,104 +4169,114 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>365.379</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>351.376</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>56.89999999999999</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>22</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>21.1</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>-5.16</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">  His friend is nowhere to be seen.  Disappointed, the boy abandons the ball and slowly leaves the dream.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.02099465590576944</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>0.03080120937263794</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.05648748616558965</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.02995547680705102</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0.03205737296954889</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.08395209332253979</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.05210138120585881</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.07495210727969349</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>0.04312570145903479</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>0.0684012148543041</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>2</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>0.1842357850808555</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.1116339869281046</v>
       </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
         <v>0.05214470284237727</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>0.02127659574468085</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>0.1242424242424242</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>0.1563390313390313</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>0.01801801801801802</v>
       </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
         <v>0.1296296296296296</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>0.08751393534002229</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>0.04065040650406504</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>0.02222222222222222</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AH33" t="n">
         <v>0.004938271604938272</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AI33" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3954,104 +4284,114 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>381.118</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>366.2</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>100</v>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">  He sleeps the rest of the night.  In the morning, the boy's father wakes up and calls for him from the bottom of the stairs.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.03885630498533725</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.04067892275439446</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.09952842298443879</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.03483606557377049</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>0.06939024390243903</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.03467469283417168</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
         <v>0.07323232323232323</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>0.06307667034762213</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>0.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>0.06818181818181819</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.05128205128205129</v>
       </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
         <v>0.0837121212121212</v>
       </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
         <v>0.05314009661835748</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.1918456918456919</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
         <v>0.09135802469135802</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
         <v>0.07631578947368421</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>0.1546218487394958</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>0.05172413793103448</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>0.1283735184663977</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>0.121587186021114</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4059,104 +4399,114 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>390.083</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>381.718</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>100</v>
       </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy wakes up, gets out of bed, and walks downstairs.  Father and son exchange a few words and the boy heads out.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.02123315639036341</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.03173821894084404</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.05514744972949307</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.01005025125628141</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.02719674331990819</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.1116490373125318</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.03299782994333497</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.03010584307961513</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>0.05403544963586372</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.05711322139664684</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>3</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>0.03870967741935484</v>
       </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
         <v>0.0175</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>0.03636363636363636</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>0.1369435817805383</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>0.3543799255427162</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>0.01025641025641026</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>0.0741437415706602</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
         <v>0.129789159526331</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>0.05681114551083592</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AE35" t="n">
         <v>0.1117270448849396</v>
       </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
       <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0.04962121212121212</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>0.7142857142857143</v>
       </c>
     </row>
@@ -4164,104 +4514,114 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>404.547</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>390.584</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>100</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy walks to the playground where his ball is still sitting at the far end of the yard.  The boy enters the playground, closing the gate after himself.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>0.04093567251461989</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.02514101531023368</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>0.1139438956422954</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.0599674916151145</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.05576646566772192</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>0.07505757913105347</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.06700056386476089</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
         <v>0.1521076688674454</v>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>0.05056179775280899</v>
       </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
       <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.03741496598639456</v>
       </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
         <v>0.1471861471861472</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>0.04906204906204906</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>0.1451377485860245</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
         <v>0.1488716992173214</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
         <v>0.07977885988357193</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AG36" t="n">
         <v>0.02531645569620253</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AH36" t="n">
         <v>0.06176717729946352</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -4269,46 +4629,50 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>418.984</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>406.591</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>100</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">  He forlornly walks to the single ball.  He slowly and unenthusiastically kicks the ball halfway down the yard.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.1292517006802721</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.1167883211678832</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.1027397260273972</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
@@ -4319,44 +4683,44 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
       <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
         <v>0.1454545454545454</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>0.1636363636363636</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>0.196078431372549</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>0.1730769230769231</v>
       </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
         <v>0.2391304347826087</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
       <c r="AD37" t="n">
         <v>0</v>
       </c>
@@ -4364,9 +4728,15 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>0.08163265306122448</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -4374,104 +4744,114 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>429.47</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>421.891</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>72.39999999999999</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
         <v>27.6</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>81.26000000000001</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve">  As he kicks the ball again, his mysterious friend from the dream appears and sneaks towards the playground.  He checks that his friend is there.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.03906641945686552</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>0.06850546279117706</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.08731592376565514</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>0.07265877162428887</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>0.06689388684238036</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.03130081300813008</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.04533333333333333</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.01333333333333334</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.04406779661016949</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.3139113428943937</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.1683600713012477</v>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>0.0853644901610018</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>0.03191489361702127</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Y38" t="n">
         <v>0.1668831168831169</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>0.2138157894736842</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA38" t="n">
         <v>0.02702702702702703</v>
       </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
         <v>0.06746031746031746</v>
       </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
         <v>0.0119047619047619</v>
       </c>
-      <c r="AF38" t="n">
+      <c r="AH38" t="n">
         <v>0.04714285714285715</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -4479,67 +4859,71 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>436.466</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>429.67</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>100</v>
       </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">  He quietly opens the gate.  He sneaks up on the boy who still doesn't see him.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>0.1153846153846154</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.06140350877192983</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>0.1194117647058824</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.02238805970149254</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.08108108108108107</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.06363636363636363</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>0.07263157894736842</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
@@ -4577,6 +4961,12 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4584,104 +4974,114 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>444.98</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>436.607</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>82.19999999999999</v>
       </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
         <v>17.8</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>74.3</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">  He taps the boy on the shoulder.  The boy whirls around.  The two friends talk back and forth.  The boy races to get his ball as his friend gets in position.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.01973262471577678</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>0.05309968116744819</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.1136064999463147</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.04378711506989069</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.02678253890460766</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.125155295082134</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.02964905203711173</v>
       </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
         <v>0.04507836990595611</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>0.03959666608381419</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>2.5</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>0.1611258055853921</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.1976897359258004</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>0.1988561933500374</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>0.07001150086256469</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>0.109549587513574</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>0.2547083200085279</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>0.03137065637065637</v>
       </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
         <v>0.08720347477447377</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.06597222222222222</v>
       </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
         <v>0.01282051282051282</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AI40" t="n">
         <v>0.4</v>
       </c>
     </row>
